--- a/papers.xlsx
+++ b/papers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/grady/Documents/personal-website/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grady\Documents\website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071F5346-0BD7-9F48-9F8F-031C0B15F59F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C933E3A1-6EBF-491A-A483-D911BD62AEF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1680" windowWidth="28800" windowHeight="15380" xr2:uid="{97D96D2E-9D3E-43F7-890C-EE13786D0DA2}"/>
+    <workbookView xWindow="7390" yWindow="3780" windowWidth="28800" windowHeight="15370" xr2:uid="{97D96D2E-9D3E-43F7-890C-EE13786D0DA2}"/>
   </bookViews>
   <sheets>
     <sheet name="Working Papers" sheetId="1" r:id="rId1"/>
@@ -140,10 +140,10 @@
     <t>&lt;b&gt;Job Market Paper&lt;/b&gt; &lt;br&gt; Coverage: &lt;a href="https://blogs.worldbank.org/en/impactevaluations/when-risk-aversion-keeps-firms-small--evidence-from-kenyan-retai0"&gt;World Bank Development Impact&lt;/a&gt;, &lt;a href="https://theeconomicmisfit.com/2026/02/13/can-firm-risk-aversion-undermine-retail-markets-in-developing-countries/"&gt;The Economic Misfit&lt;/a&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Economists often study non-market goods such as health and air quality. This paper introduces a new method to estimate demand for such amenities and applies it to measure the value of a statistical life (VSL) in Kenya. My approach is to update beliefs about the life-saving efficacy of a product (a motorcycle helmet) and elicit product choice. This generates instruments allowing one to use subjective beliefs to estimate demand, rather than assuming rational expectations. This method does not require beliefs to be reported error-free but does require classical mismeasurement. I validate this assumption using features of the experimental design. The estimated VSL is \$523, near the left tail of Kenyan estimates. Standard methods for estimating VSL produce skewed results, driven by severe violations of rational expectations. These findings help explain low observed demand for many health products and suggest that directing more development aid towards consumption may increase welfare. </t>
-  </si>
-  <si>
     <t>with Michael Walker, Nick Shankar, Edward Miguel and Dennis Egger &lt;br&gt; &lt;i&gt; Revise and Resubmit at the Journal of Political Economy &lt;/i&gt;Coverage: &lt;a href="https://www.nytimes.com/2025/08/18/health/cash-transfer-kenya-poverty.html"&gt;New York Times&lt;/a&gt;, &lt;a href="https://www.npr.org/2025/08/18/nx-s1-5498591/cash-payments-cut-infant-mortality-in-rural-kenya-by-half"&gt;NPR&lt;/a&gt;, &lt;a href="https://www.theguardian.com/global-development/2025/oct/09/money-direct-cash-transfers-women-rural-kenya-a-new-life"&gt;The Guardian&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>This paper introduces a method to estimate demand for non-market goods, such as safety and environmental quality. I experimentally update beliefs about how a product affects exposure to a non-market good, then examine how willingness to pay for the product changes. This identifies demand for the non-market good without assuming rational expectations. Beliefs need not be reported accurately, only with classical error, which I test using the design. I apply the method to the value of a statistical life (VSL) in Kenya by updating beliefs about motorcycle helmet effectiveness. First, I estimate a VSL of \$523, below policy values but near academic estimates. Second, I document violations of rational expectations that bias conventional estimators. Third, the VSL is rationalized by differences in the marginal utility of consumption with income. This indicates that applying recipient VSLs to foreign aid understates welfare gains, since program funders have lower marginal utility of consumption.</t>
   </si>
 </sst>
 </file>
@@ -540,15 +540,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8F856E6-0DAE-4AB0-8DFD-4ED5A926F3C8}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.1640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="38.5" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="1"/>
+    <col min="1" max="1" width="28.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.1796875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="38.453125" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -565,7 +565,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -582,12 +582,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="350" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="348" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>16</v>
@@ -596,12 +596,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="380" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="377" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>23</v>
@@ -626,15 +626,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4634DBF9-2A4B-4BD6-9503-80AC50EBF305}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.1640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="38.5" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="1"/>
+    <col min="1" max="1" width="28.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.1796875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="38.453125" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -651,7 +651,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="335" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="348" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -676,15 +676,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72C59CF-0C37-4915-9D99-95832D380190}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.1640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="38.5" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="1"/>
+    <col min="1" max="1" width="28.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.1796875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="38.453125" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -701,7 +701,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -712,7 +712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="391.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>20</v>
       </c>

--- a/papers.xlsx
+++ b/papers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grady\Documents\website\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gkilleen/Documents/personal-website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C933E3A1-6EBF-491A-A483-D911BD62AEF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C69F31F9-93E5-594E-ABDC-6287B75D6A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7390" yWindow="3780" windowWidth="28800" windowHeight="15370" xr2:uid="{97D96D2E-9D3E-43F7-890C-EE13786D0DA2}"/>
+    <workbookView xWindow="1440" yWindow="3080" windowWidth="28800" windowHeight="15380" xr2:uid="{97D96D2E-9D3E-43F7-890C-EE13786D0DA2}"/>
   </bookViews>
   <sheets>
     <sheet name="Working Papers" sheetId="1" r:id="rId1"/>
@@ -134,9 +134,6 @@
     <t xml:space="preserve">We estimate the impacts of large-scale unconditional cash transfers on child survival. One-time transfers of USD 1000 were provided to over 10,500 poor households across 653 randomized villages in Kenya. We collected census data on over 100,000 births, including on mortality and cause of death, and detailed data on health behaviors. Unconditional cash transfers (accounting for spillovers) lead to 48\% fewer infant deaths before age one and 45\% fewer child deaths before age five. These improvements appear to arise from better maternal health and nutrition, a 53\% reduction in labor supply around the time of childbirth, and a 45\% increase in hospital delivery. There is a transient 10\% increase in fertility, but mortality reductions are largest in households receiving transfers after pregnancies began, ruling out selection bias. Mortality effects dissipate rapidly when cash is distributed more than three months from the birth. Mortality reductions are concentrated among households with limited (monetary) consumption gains,  suggesting a trade-off between financial and health investments. </t>
   </si>
   <si>
-    <t xml:space="preserve">This paper studies whether risk aversion prevents firms in low and middle-income economies from making profitable but uncertain investments. While economists typically model firms as risk neutral, I posit that this assumption is unlikely to hold for the modal developing-country firm, which is owner-operated, meaning business losses threaten owners' consumption. I develop a model showing how risk aversion can reduce firms’ willingness to experiment with new technologies. I test the model’s predictions within the context of retailers' decision to adopt and sell a new product using two field experiments with over 1,200 Kenyan firms. First, offering firms an insurance contract that creates a mean-preserving contraction of profits increases adoption by 50\%. Second, a temporary supplier returns policy increases post-intervention stocking by 70\%. These persistent effects arise through a reduction in the variance of beliefs, not changes in expected profits. Third, increasing the continuation value of learning expands adoption by 80\%. These results show that a feature of developing economies -- small firms in the presence of incomplete financial markets -- creates a barrier to firm growth. Furthermore, the findings suggest that risk aversion constrains the retail market for new products, harming incentives for companies to introduce goods in developing countries. </t>
-  </si>
-  <si>
     <t>&lt;b&gt;Job Market Paper&lt;/b&gt; &lt;br&gt; Coverage: &lt;a href="https://blogs.worldbank.org/en/impactevaluations/when-risk-aversion-keeps-firms-small--evidence-from-kenyan-retai0"&gt;World Bank Development Impact&lt;/a&gt;, &lt;a href="https://theeconomicmisfit.com/2026/02/13/can-firm-risk-aversion-undermine-retail-markets-in-developing-countries/"&gt;The Economic Misfit&lt;/a&gt;</t>
   </si>
   <si>
@@ -144,6 +141,9 @@
   </si>
   <si>
     <t>This paper introduces a method to estimate demand for non-market goods, such as safety and environmental quality. I experimentally update beliefs about how a product affects exposure to a non-market good, then examine how willingness to pay for the product changes. This identifies demand for the non-market good without assuming rational expectations. Beliefs need not be reported accurately, only with classical error, which I test using the design. I apply the method to the value of a statistical life (VSL) in Kenya by updating beliefs about motorcycle helmet effectiveness. First, I estimate a VSL of \$523, below policy values but near academic estimates. Second, I document violations of rational expectations that bias conventional estimators. Third, the VSL is rationalized by differences in the marginal utility of consumption with income. This indicates that applying recipient VSLs to foreign aid understates welfare gains, since program funders have lower marginal utility of consumption.</t>
+  </si>
+  <si>
+    <t>Does risk aversion prevent firms in developing economies from making profitable but uncertain investments? Using a model and two field experiments with over 1,200 Kenyan firms, I study retailers' decisions to stock a new consumer product. First, an insurance contract that is strictly dominated under risk neutrality increases adoption from 20\% to 30\%. Second, a temporary supplier returns policy increases post-intervention stocking by 70\%, through reduced belief uncertainty rather than higher expected profits. Third, increasing the continuation value of learning expands adoption by 88\%. Results indicate that risk aversion constrains firm experimentation, limiting the retail diffusion of new products.</t>
   </si>
 </sst>
 </file>
@@ -540,15 +540,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8F856E6-0DAE-4AB0-8DFD-4ED5A926F3C8}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.81640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.1796875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="38.453125" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.81640625" style="1"/>
+    <col min="1" max="1" width="28.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.1640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="38.5" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -565,15 +565,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="256" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>17</v>
@@ -582,12 +582,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="348" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="350" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>16</v>
@@ -596,12 +596,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="377" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="380" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>23</v>
@@ -626,15 +626,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4634DBF9-2A4B-4BD6-9503-80AC50EBF305}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.81640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.1796875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="38.453125" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.81640625" style="1"/>
+    <col min="1" max="1" width="28.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.1640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="38.5" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -651,7 +651,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="348" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="335" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -676,15 +676,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72C59CF-0C37-4915-9D99-95832D380190}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.81640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.1796875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="38.453125" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.81640625" style="1"/>
+    <col min="1" max="1" width="28.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.1640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="38.5" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -701,7 +701,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -712,7 +712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="391.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>20</v>
       </c>

--- a/papers.xlsx
+++ b/papers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gkilleen/Documents/personal-website/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grady Killeen\Documents\website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C69F31F9-93E5-594E-ABDC-6287B75D6A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89ED302-14FA-438C-8A1C-0B1FBFA825A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="3080" windowWidth="28800" windowHeight="15380" xr2:uid="{97D96D2E-9D3E-43F7-890C-EE13786D0DA2}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{97D96D2E-9D3E-43F7-890C-EE13786D0DA2}"/>
   </bookViews>
   <sheets>
     <sheet name="Working Papers" sheetId="1" r:id="rId1"/>
@@ -140,10 +140,10 @@
     <t>with Michael Walker, Nick Shankar, Edward Miguel and Dennis Egger &lt;br&gt; &lt;i&gt; Revise and Resubmit at the Journal of Political Economy &lt;/i&gt;Coverage: &lt;a href="https://www.nytimes.com/2025/08/18/health/cash-transfer-kenya-poverty.html"&gt;New York Times&lt;/a&gt;, &lt;a href="https://www.npr.org/2025/08/18/nx-s1-5498591/cash-payments-cut-infant-mortality-in-rural-kenya-by-half"&gt;NPR&lt;/a&gt;, &lt;a href="https://www.theguardian.com/global-development/2025/oct/09/money-direct-cash-transfers-women-rural-kenya-a-new-life"&gt;The Guardian&lt;/a&gt;</t>
   </si>
   <si>
-    <t>This paper introduces a method to estimate demand for non-market goods, such as safety and environmental quality. I experimentally update beliefs about how a product affects exposure to a non-market good, then examine how willingness to pay for the product changes. This identifies demand for the non-market good without assuming rational expectations. Beliefs need not be reported accurately, only with classical error, which I test using the design. I apply the method to the value of a statistical life (VSL) in Kenya by updating beliefs about motorcycle helmet effectiveness. First, I estimate a VSL of \$523, below policy values but near academic estimates. Second, I document violations of rational expectations that bias conventional estimators. Third, the VSL is rationalized by differences in the marginal utility of consumption with income. This indicates that applying recipient VSLs to foreign aid understates welfare gains, since program funders have lower marginal utility of consumption.</t>
-  </si>
-  <si>
     <t>Does risk aversion prevent firms in developing economies from making profitable but uncertain investments? Using a model and two field experiments with over 1,200 Kenyan firms, I study retailers' decisions to stock a new consumer product. First, an insurance contract that is strictly dominated under risk neutrality increases adoption from 20\% to 30\%. Second, a temporary supplier returns policy increases post-intervention stocking by 70\%, through reduced belief uncertainty rather than higher expected profits. Third, increasing the continuation value of learning expands adoption by 88\%. Results indicate that risk aversion constrains firm experimentation, limiting the retail diffusion of new products.</t>
+  </si>
+  <si>
+    <t>This paper introduces a new method for estimating demand for non-market goods and applies it to the value of a statistical life (VSL) in Kenya. The approach updates beliefs about the life-saving efficacy of a product (helmets) and elicits product choice. This allows demand to be estimated from subjective beliefs rather than assuming rational expectations. The resulting VSL estimate is \$523, near the lower end of Kenyan estimates. Standard methods produce skewed results, driven by violations of rational expectations. The findings rationalize weak demand for preventive health and highlight limited evidence and theoretical support for VSLs used in benefit-cost analysis.</t>
   </si>
 </sst>
 </file>
@@ -540,15 +540,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8F856E6-0DAE-4AB0-8DFD-4ED5A926F3C8}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.1640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="38.5" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="1"/>
+    <col min="1" max="1" width="28.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.109375" style="1" customWidth="1"/>
+    <col min="3" max="4" width="38.44140625" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -565,7 +565,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="256" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -573,7 +573,7 @@
         <v>24</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>17</v>
@@ -582,12 +582,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="350" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>16</v>
@@ -596,7 +596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="380" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="360" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -626,15 +626,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4634DBF9-2A4B-4BD6-9503-80AC50EBF305}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.1640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="38.5" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="1"/>
+    <col min="1" max="1" width="28.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.109375" style="1" customWidth="1"/>
+    <col min="3" max="4" width="38.44140625" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -651,7 +651,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="335" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -676,15 +676,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72C59CF-0C37-4915-9D99-95832D380190}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.1640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="38.5" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="1"/>
+    <col min="1" max="1" width="28.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.109375" style="1" customWidth="1"/>
+    <col min="3" max="4" width="38.44140625" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -701,7 +701,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -712,7 +712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>20</v>
       </c>

--- a/papers.xlsx
+++ b/papers.xlsx
@@ -1,183 +1,54 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grady Killeen\Documents\website\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89ED302-14FA-438C-8A1C-0B1FBFA825A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{97D96D2E-9D3E-43F7-890C-EE13786D0DA2}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Working Papers" sheetId="1" r:id="rId1"/>
-    <sheet name="Publications" sheetId="2" r:id="rId2"/>
-    <sheet name="Work in Progress" sheetId="3" r:id="rId3"/>
+    <sheet name="Working Papers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Publications" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Work in Progress" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Authors</t>
-  </si>
-  <si>
-    <t>Link</t>
-  </si>
-  <si>
-    <t>Abstract</t>
-  </si>
-  <si>
-    <t>Using satellites and phones to evaluate and promote agricultural technology adoption: Evidence from smallholder farms in India</t>
-  </si>
-  <si>
-    <t>This paper evaluates a low-cost, customized soil nutrient management advisory service in India. As a methodological contribution, we examine whether and in which settings satellite measurements may be effective at estimating both agricultural yields and treatment effects. The intervention improves self-reported fertilizer management practices, though not enough to measurably affect yields. Satellite measurements calibrated using OLS produce more precise point estimates than farmer-reported data, suggesting power gains. However, linear models, common in the literature, likely produce biased estimates. We propose an alternative procedure, using two-stage least squares. In settings without attrition, this approach obtains lower statistical power than self-reported yields; in settings with differential attrition, it may substantially increase power. We include a “cookbook” and code that should allow other researchers to use remote sensing for yield estimation and program evaluation.</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.jdeveco.2025.103463</t>
-  </si>
-  <si>
-    <t>Free-Riding and New Product Adoption: Evidence from Burundi</t>
-  </si>
-  <si>
-    <t>Multiple Missing Markets and Allocative Efficiency</t>
-  </si>
-  <si>
-    <t>with Supreet Kaur</t>
-  </si>
-  <si>
-    <t>Latex</t>
-  </si>
-  <si>
-    <t>Can Cash Transfers Save Lives? Evidence from a Large-Scale Experiment in Kenya</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Data collection in process </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>with Luisa Cefala, Rédempteur Ntawiratsa and Nicholas Swanson</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">In low and middle-income (LMIC) countries, businesses often use technologies inside the frontier, innovate less, and slowly adopt new products and technologies (Cirera et al. 2022). The reasons for these facts are not well understood, particularly for small and microenterprises (e.g. Atkin et al. 2017). 
-We investigate whether a lack of institutions to protect the value of intellectual property contributes to these facts. High-income economies tend to have strong patent systems to promote discoveries, and regulators permit exclusive dealing in retail environments due to similar forces. But LMIC firms are often informal and undifferentiated, meaning neighbours are likely to adopt discoveries of their competitors without compensation. 
-This project focuses on this problem in the case of retail firms’ decision to adopt a new product-- a setting where firms face risk ex-ante because they do not know if demand will exist, but, ex-post, competitors can learn if demand is high by observing the first mover. We examine whether offering retailers exclusive access to supply of a new product promotes adoption. Our study also tests whether firms are colluding so that if there is a null result we can understand if it is due to collusion, a possible upside to the finding that some markets in LMICs are uncompetitive (Bergquist and Dinerstein 2020). </t>
-  </si>
-  <si>
-    <t>A New Experimental Method for Estimating Demand for Non-market Goods: With an Application to the Value of a Statistical Life</t>
-  </si>
-  <si>
-    <t>with Shawn Cole, Aparna Krishna and Tomoko Harigaya. Journal of Development Economics.</t>
-  </si>
-  <si>
-    <t>https://gkilleen33.github.io/papers/working/Killeen-VSL.pdf</t>
-  </si>
-  <si>
-    <t>https://gkilleen33.github.io/papers/working/Killeen-JMP.pdf</t>
-  </si>
-  <si>
-    <t>https://gkilleen33.github.io/papers/working/GE-IMR.pdf</t>
-  </si>
-  <si>
-    <t>Risk Aversion and Barriers to Firm Growth: Experimental Evidence from Small Retailers</t>
-  </si>
-  <si>
-    <t>The Long-run Effects of Unconditional Cash Transfers: Evidence from the Kenya General Equilibrium Study</t>
-  </si>
-  <si>
-    <t>with Dennis Egger, Edward Miguel and Michael Walker</t>
-  </si>
-  <si>
-    <t>Recent studies document positive short-run effects of unconditional cash transfers (UCTs) on cash recipients and spillover effects on non-recipients. But modest sample sizes and challenges with tracking households over time have limited research on the long-run effects of UCTs. We study the long-run effects of the Kenya General Equilibrium Study (KGES) on recipient households and the local economy using census and survey data collected up to ten years post-transfers. An “endline 2” completed 4-7 years after the transfers collected census data from each household and enterprise in the study area, and a representative survey of more than 10,000 households and firms obtained more detailed consumption and production measures for a subset, including from those that migrated out of the study area. We collected this same information in an “endline 3” completed 7-10 years after the experimental start. Preliminary results from endline 2 show persistent consumption gains among recipients and expansion of non-farm enterprise revenue. Ongoing analysis examines whether these effects persisted to endline 3 and aims to estimate long-run transfer multipliers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">We estimate the impacts of large-scale unconditional cash transfers on child survival. One-time transfers of USD 1000 were provided to over 10,500 poor households across 653 randomized villages in Kenya. We collected census data on over 100,000 births, including on mortality and cause of death, and detailed data on health behaviors. Unconditional cash transfers (accounting for spillovers) lead to 48\% fewer infant deaths before age one and 45\% fewer child deaths before age five. These improvements appear to arise from better maternal health and nutrition, a 53\% reduction in labor supply around the time of childbirth, and a 45\% increase in hospital delivery. There is a transient 10\% increase in fertility, but mortality reductions are largest in households receiving transfers after pregnancies began, ruling out selection bias. Mortality effects dissipate rapidly when cash is distributed more than three months from the birth. Mortality reductions are concentrated among households with limited (monetary) consumption gains,  suggesting a trade-off between financial and health investments. </t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Job Market Paper&lt;/b&gt; &lt;br&gt; Coverage: &lt;a href="https://blogs.worldbank.org/en/impactevaluations/when-risk-aversion-keeps-firms-small--evidence-from-kenyan-retai0"&gt;World Bank Development Impact&lt;/a&gt;, &lt;a href="https://theeconomicmisfit.com/2026/02/13/can-firm-risk-aversion-undermine-retail-markets-in-developing-countries/"&gt;The Economic Misfit&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>with Michael Walker, Nick Shankar, Edward Miguel and Dennis Egger &lt;br&gt; &lt;i&gt; Revise and Resubmit at the Journal of Political Economy &lt;/i&gt;Coverage: &lt;a href="https://www.nytimes.com/2025/08/18/health/cash-transfer-kenya-poverty.html"&gt;New York Times&lt;/a&gt;, &lt;a href="https://www.npr.org/2025/08/18/nx-s1-5498591/cash-payments-cut-infant-mortality-in-rural-kenya-by-half"&gt;NPR&lt;/a&gt;, &lt;a href="https://www.theguardian.com/global-development/2025/oct/09/money-direct-cash-transfers-women-rural-kenya-a-new-life"&gt;The Guardian&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>Does risk aversion prevent firms in developing economies from making profitable but uncertain investments? Using a model and two field experiments with over 1,200 Kenyan firms, I study retailers' decisions to stock a new consumer product. First, an insurance contract that is strictly dominated under risk neutrality increases adoption from 20\% to 30\%. Second, a temporary supplier returns policy increases post-intervention stocking by 70\%, through reduced belief uncertainty rather than higher expected profits. Third, increasing the continuation value of learning expands adoption by 88\%. Results indicate that risk aversion constrains firm experimentation, limiting the retail diffusion of new products.</t>
-  </si>
-  <si>
-    <t>This paper introduces a new method for estimating demand for non-market goods and applies it to the value of a statistical life (VSL) in Kenya. The approach updates beliefs about the life-saving efficacy of a product (helmets) and elicits product choice. This allows demand to be estimated from subjective beliefs rather than assuming rational expectations. The resulting VSL estimate is \$523, near the lower end of Kenyan estimates. Standard methods produce skewed results, driven by violations of rational expectations. The findings rationalize weak demand for preventive health and highlight limited evidence and theoretical support for VSLs used in benefit-cost analysis.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <i val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -194,31 +65,91 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -538,197 +469,391 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8F856E6-0DAE-4AB0-8DFD-4ED5A926F3C8}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="28.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.109375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="38.44140625" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.77734375" style="1"/>
+    <col width="60" customWidth="1" style="1" min="1" max="1"/>
+    <col width="45" customWidth="1" style="1" min="2" max="2"/>
+    <col width="40" customWidth="1" style="1" min="3" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" style="1" min="5" max="16384"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Authors</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Links</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Latex</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="244.8" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Risk Aversion and Barriers to Firm Growth: Experimental Evidence from Small Retailers</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Job Market Paper</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://blogs.worldbank.org/en/impactevaluations/when-risk-aversion-keeps-firms-small--evidence-from-kenyan-retai0"&gt;World Bank Development Impact&lt;/a&gt;, &lt;a href="https://theeconomicmisfit.com/2026/02/13/can-firm-risk-aversion-undermine-retail-markets-in-developing-countries/"&gt;The Economic Misfit&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Does risk aversion prevent firms in developing economies from making profitable but uncertain investments? Using a model and two field experiments with over 1,200 Kenyan firms, I study retailers' decisions to stock a new consumer product. First, an insurance contract that is strictly dominated under risk neutrality increases adoption from 20\% to 30\%. Second, a temporary supplier returns policy increases post-intervention stocking by 70\%, through reduced belief uncertainty rather than higher expected profits. Third, increasing the continuation value of learning expands adoption by 88\%. Results indicate that risk aversion constrains firm experimentation, limiting the retail diffusion of new products.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://gkilleen33.github.io/papers/working/Killeen-JMP.pdf</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="1">
+      <c r="I2" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="1">
+    <row r="3" ht="230.4" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A New Experimental Method for Estimating Demand for Non-market Goods: With an Application to the Value of a Statistical Life</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>This paper introduces a new method for estimating demand for non-market goods and applies it to the value of a statistical life (VSL) in Kenya. The approach updates beliefs about the life-saving efficacy of a product (helmets) and elicits product choice. This allows demand to be estimated from subjective beliefs rather than assuming rational expectations. The resulting VSL estimate is \$523, near the lower end of Kenyan estimates. Standard methods produce skewed results, driven by violations of rational expectations. The findings rationalize weak demand for preventive health and highlight limited evidence and theoretical support for VSLs used in benefit-cost analysis.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://gkilleen33.github.io/papers/working/Killeen-VSL.pdf</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="360" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="I3" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="4" ht="360" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Can Cash Transfers Save Lives? Evidence from a Large-Scale Experiment in Kenya</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>with Michael Walker, Nick Shankar, Edward Miguel and Dennis Egger</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Revise and Resubmit, &lt;i&gt;Journal of Political Economy&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>&lt;a href="https://www.nytimes.com/2025/08/18/health/cash-transfer-kenya-poverty.html"&gt;New York Times&lt;/a&gt;, &lt;a href="https://www.npr.org/2025/08/18/nx-s1-5498591/cash-payments-cut-infant-mortality-in-rural-kenya-by-half"&gt;NPR&lt;/a&gt;, &lt;a href="https://www.theguardian.com/global-development/2025/oct/09/money-direct-cash-transfers-women-rural-kenya-a-new-life"&gt;The Guardian&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">We estimate the impacts of large-scale unconditional cash transfers on child survival. One-time transfers of USD 1000 were provided to over 10,500 poor households across 653 randomized villages in Kenya. We collected census data on over 100,000 births, including on mortality and cause of death, and detailed data on health behaviors. Unconditional cash transfers (accounting for spillovers) lead to 48\% fewer infant deaths before age one and 45\% fewer child deaths before age five. These improvements appear to arise from better maternal health and nutrition, a 53\% reduction in labor supply around the time of childbirth, and a 45\% increase in hospital delivery. There is a transient 10\% increase in fertility, but mortality reductions are largest in households receiving transfers after pregnancies began, ruling out selection bias. Mortality effects dissipate rapidly when cash is distributed more than three months from the birth. Mortality reductions are concentrated among households with limited (monetary) consumption gains,  suggesting a trade-off between financial and health investments. </t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://gkilleen33.github.io/papers/working/GE-IMR.pdf</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" xr:uid="{C80A6612-84C5-4740-9FA9-F56BA622C6F1}"/>
-    <hyperlink ref="D2" r:id="rId2" xr:uid="{11D16F1B-AD82-48FA-9833-445D3F3963E4}"/>
-    <hyperlink ref="D4" r:id="rId3" xr:uid="{DFD0FFEB-B84A-4674-A8C7-B7EC4F6A8DC7}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4634DBF9-2A4B-4BD6-9503-80AC50EBF305}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="28.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.109375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="38.44140625" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.77734375" style="1"/>
+    <col width="60" customWidth="1" style="1" min="1" max="1"/>
+    <col width="45" customWidth="1" style="1" min="2" max="2"/>
+    <col width="40" customWidth="1" style="1" min="3" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" style="1" min="5" max="16384"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Authors</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Links</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Latex</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="331.2" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Using satellites and phones to evaluate and promote agricultural technology adoption: Evidence from smallholder farms in India</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>with Shawn Cole, Aparna Krishna and Tomoko Harigaya</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>&lt;i&gt;Journal of Development Economics&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>This paper evaluates a low-cost, customized soil nutrient management advisory service in India. As a methodological contribution, we examine whether and in which settings satellite measurements may be effective at estimating both agricultural yields and treatment effects. The intervention improves self-reported fertilizer management practices, though not enough to measurably affect yields. Satellite measurements calibrated using OLS produce more precise point estimates than farmer-reported data, suggesting power gains. However, linear models, common in the literature, likely produce biased estimates. We propose an alternative procedure, using two-stage least squares. In settings without attrition, this approach obtains lower statistical power than self-reported yields; in settings with differential attrition, it may substantially increase power. We include a “cookbook” and code that should allow other researchers to use remote sensing for yield estimation and program evaluation.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.jdeveco.2025.103463</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{F8D0534D-3205-4788-AD28-D1E9EEAA5F33}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72C59CF-0C37-4915-9D99-95832D380190}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="28.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.109375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="38.44140625" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.77734375" style="1"/>
+    <col width="60" customWidth="1" style="1" min="1" max="1"/>
+    <col width="45" customWidth="1" style="1" min="2" max="2"/>
+    <col width="40" customWidth="1" style="1" min="3" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" style="1" min="5" max="16384"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>22</v>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Authors</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Links</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Latex</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="409.6" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Free-Riding and New Product Adoption: Evidence from Burundi</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>with Luisa Cefala, Rédempteur Ntawiratsa and Nicholas Swanson</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Data collection in progress</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In low and middle-income (LMIC) countries, businesses often use technologies inside the frontier, innovate less, and slowly adopt new products and technologies (Cirera et al. 2022). The reasons for these facts are not well understood, particularly for small and microenterprises (e.g. Atkin et al. 2017). 
+We investigate whether a lack of institutions to protect the value of intellectual property contributes to these facts. High-income economies tend to have strong patent systems to promote discoveries, and regulators permit exclusive dealing in retail environments due to similar forces. But LMIC firms are often informal and undifferentiated, meaning neighbours are likely to adopt discoveries of their competitors without compensation. 
+This project focuses on this problem in the case of retail firms’ decision to adopt a new product-- a setting where firms face risk ex-ante because they do not know if demand will exist, but, ex-post, competitors can learn if demand is high by observing the first mover. We examine whether offering retailers exclusive access to supply of a new product promotes adoption. Our study also tests whether firms are colluding so that if there is a null result we can understand if it is due to collusion, a possible upside to the finding that some markets in LMICs are uncompetitive (Bergquist and Dinerstein 2020). </t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28.8" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Multiple Missing Markets and Allocative Efficiency</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>with Supreet Kaur</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="388.8" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>The Long-run Effects of Unconditional Cash Transfers: Evidence from the Kenya General Equilibrium Study</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>with Dennis Egger, Edward Miguel and Michael Walker</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Recent studies document positive short-run effects of unconditional cash transfers (UCTs) on cash recipients and spillover effects on non-recipients. But modest sample sizes and challenges with tracking households over time have limited research on the long-run effects of UCTs. We study the long-run effects of the Kenya General Equilibrium Study (KGES) on recipient households and the local economy using census and survey data collected up to ten years post-transfers. An “endline 2” completed 4-7 years after the transfers collected census data from each household and enterprise in the study area, and a representative survey of more than 10,000 households and firms obtained more detailed consumption and production measures for a subset, including from those that migrated out of the study area. We collected this same information in an “endline 3” completed 7-10 years after the experimental start. Preliminary results from endline 2 show persistent consumption gains among recipients and expansion of non-farm enterprise revenue. Ongoing analysis examines whether these effects persisted to endline 3 and aims to estimate long-run transfer multipliers.</t>
+        </is>
       </c>
     </row>
   </sheetData>
